--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/02_DFMEA ve Tasarım Gözden Geçirme/EKG-TAS-FRM-01_dfmea_sentezi_ve_ozel_onay_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/02_DFMEA ve Tasarım Gözden Geçirme/EKG-TAS-FRM-01_dfmea_sentezi_ve_ozel_onay_kaydi.xlsx
@@ -807,7 +807,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-FRM-01&amp;C&amp;"Arial,Regular"&amp;11DFMEA Sentezi ve Özel Onay Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Hatalı sabitli formüller kaldırıldı; tam veri girişine bağlı RPN ve kaynaklı artık risk/onay kaydı düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1000,7 +1001,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-FRM-01&amp;C&amp;"Arial,Regular"&amp;11DFMEA Sentezi ve Özel Onay Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Hatalı sabitli formüller kaldırıldı; tam veri girişine bağlı RPN ve kaynaklı artık risk/onay kaydı düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>